--- a/9434 JP.xlsx
+++ b/9434 JP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F578312-7D17-40F0-AE9F-D039E0238DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E552E8-2620-4BCF-AECA-CB851C89DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23985" yWindow="1035" windowWidth="21720" windowHeight="17280" xr2:uid="{A1FCB31D-8E75-4EBD-A372-27E5F30B4E20}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{A1FCB31D-8E75-4EBD-A372-27E5F30B4E20}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -126,6 +129,19 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -147,28 +163,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -553,21 +575,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38156278-DC79-4430-B7A5-777BCD1159CF}">
   <dimension ref="B2:K33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7265625" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K2" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J3" t="s">
         <v>1</v>
       </c>
@@ -575,16 +597,16 @@
         <v>47263.966428</v>
       </c>
     </row>
-    <row r="4" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="1">
         <f>+K2*K3</f>
-        <v>13281174.566268001</v>
-      </c>
-    </row>
-    <row r="5" spans="10:11" x14ac:dyDescent="0.2">
+        <v>9452793.2855999991</v>
+      </c>
+    </row>
+    <row r="5" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>3</v>
       </c>
@@ -593,7 +615,7 @@
         <v>4118585</v>
       </c>
     </row>
-    <row r="6" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>4</v>
       </c>
@@ -602,31 +624,31 @@
         <v>6215808</v>
       </c>
     </row>
-    <row r="7" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="1">
         <f>+K4-K5+K6</f>
-        <v>15378397.566268001</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+        <v>11550016.285599999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>23</v>
       </c>
@@ -640,179 +662,185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3712CA0-E553-4718-9758-1D7FD41ECD02}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="6" customWidth="1"/>
+    <col min="3" max="4" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C2" s="4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C2" s="10">
         <v>45291</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="10">
         <v>45657</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="11">
         <v>45747</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="9">
         <v>455.6</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="9">
         <v>616</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="9">
         <v>170.9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="9">
         <v>203.6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="9">
         <v>1199.5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="9">
         <v>1252.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="9">
         <v>610</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="9">
         <v>673.6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="9">
         <v>191.6</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="9">
         <v>184.2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="9">
         <v>301.8</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="9">
         <v>305.39999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="9">
         <v>1644.8</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="9">
         <v>1666.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>4511.6000000000004</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>4811.5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="2">
         <f>6350-D10</f>
         <v>1538.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="9">
         <v>731.9</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="9">
         <v>821.9</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="8">
         <f>950-D11</f>
         <v>128.10000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="9">
         <v>406.7</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="9">
         <v>436.6</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="8">
         <f>510-D12</f>
         <v>73.399999999999977</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="9">
         <v>1309.0999999999999</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="9">
         <v>1371.8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="7">
         <v>443.9</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="7">
         <v>540.9</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{5DE04C96-3E4D-4646-BBF6-76C7EFCC16B7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>